--- a/tests/fixtures/squad-template/County-29.xlsx
+++ b/tests/fixtures/squad-template/County-29.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,11 +508,6 @@
           <t>Player Name *</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Default No.</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -520,9 +515,6 @@
           <t>Aria Alder</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -530,9 +522,6 @@
           <t>Bella Birch</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -540,9 +529,6 @@
           <t>Cora Cedar</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,9 +536,6 @@
           <t>Dara Dale</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -560,9 +543,6 @@
           <t>Ella Elm</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -570,9 +550,6 @@
           <t>Fia Field</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -580,9 +557,6 @@
           <t>Grace Grove</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,9 +564,6 @@
           <t>Hana Hazel</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -600,9 +571,6 @@
           <t>Ivy Iris</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -610,9 +578,6 @@
           <t>Jade Juniper</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -620,9 +585,6 @@
           <t>Kara Lake</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -630,9 +592,6 @@
           <t>Lena Linden</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -640,9 +599,6 @@
           <t>Mara Maple</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -650,9 +606,6 @@
           <t>Nessa Oak</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -660,9 +613,6 @@
           <t>Orla Pine</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -670,9 +620,6 @@
           <t>Pia Reed</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -680,9 +627,6 @@
           <t>Rosa Rowan</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>17</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -690,9 +634,6 @@
           <t>Sara Sage</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -700,9 +641,6 @@
           <t>Tara Stone</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>19</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -710,9 +648,6 @@
           <t>Una Vale</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -720,9 +655,6 @@
           <t>Vera Willow</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -730,9 +662,6 @@
           <t>Willa Wood</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>22</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -740,9 +669,6 @@
           <t>Yara Ash</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -750,9 +676,6 @@
           <t>Zara Bay</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>24</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -760,9 +683,6 @@
           <t>Ada Brook</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -770,9 +690,6 @@
           <t>Bea Fern</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>26</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -780,9 +697,6 @@
           <t>Cara Hill</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>27</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -790,9 +704,6 @@
           <t>Dee Moss</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -800,53 +711,39 @@
           <t>Eva Park</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>29</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
-      <c r="B31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
-      <c r="B32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
-      <c r="B33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n"/>
-      <c r="B34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n"/>
-      <c r="B35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
-      <c r="B36" s="1" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n"/>
-      <c r="B37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
-      <c r="B38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n"/>
-      <c r="B39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
-      <c r="B40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n"/>
-      <c r="B41" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
